--- a/data/trans_orig/IP16CS1_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP16CS1_2023-Clase-trans_orig.xlsx
@@ -730,7 +730,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>345</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -745,7 +745,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>15,49%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>278</t>
+          <t>134</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
@@ -780,7 +780,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -800,7 +800,7 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1143</t>
+          <t>974</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
@@ -815,7 +815,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>26,41%</t>
+          <t>22,51%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2858</t>
+          <t>2603</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>66,03%</t>
+          <t>60,15%</t>
         </is>
       </c>
     </row>
@@ -1257,7 +1257,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2889</t>
+          <t>2893</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>66,76%</t>
+          <t>66,85%</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>12,44%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>369</t>
+          <t>401</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -1462,7 +1462,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>17,58%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1579</t>
+          <t>1516</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5486</t>
+          <t>5276</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>26,18%</t>
+          <t>25,14%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>90,98%</t>
+          <t>87,5%</t>
         </is>
       </c>
     </row>
@@ -1643,7 +1643,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3749</t>
+          <t>3283</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>87,56%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1713,7 +1713,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>3957</t>
+          <t>3890</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>65,63%</t>
+          <t>64,51%</t>
         </is>
       </c>
     </row>
@@ -1791,7 +1791,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1813</t>
+          <t>1912</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1806,7 +1806,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>79,5%</t>
+          <t>83,81%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2332</t>
+          <t>2204</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1841,7 +1841,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>38,68%</t>
+          <t>36,55%</t>
         </is>
       </c>
     </row>
@@ -1904,7 +1904,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1314</t>
+          <t>1710</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1919,7 +1919,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>57,6%</t>
+          <t>74,97%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1939,7 +1939,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1809</t>
+          <t>1775</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1954,7 +1954,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>29,99%</t>
+          <t>29,44%</t>
         </is>
       </c>
     </row>
@@ -2811,7 +2811,7 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1470</t>
+          <t>1356</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>30,43%</t>
+          <t>28,06%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -2846,7 +2846,7 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3297</t>
+          <t>3421</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
@@ -2861,7 +2861,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>48,59%</t>
+          <t>50,42%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -3268,7 +3268,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3363</t>
+          <t>3476</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>69,61%</t>
+          <t>71,94%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3489</t>
+          <t>3367</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3318,7 +3318,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>51,41%</t>
+          <t>49,62%</t>
         </is>
       </c>
     </row>
@@ -3528,7 +3528,7 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1199</t>
+          <t>1467</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
@@ -3543,7 +3543,7 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>32,17%</t>
+          <t>39,37%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1849</t>
+          <t>1511</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3661,7 +3661,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>49,62%</t>
+          <t>40,56%</t>
         </is>
       </c>
     </row>
@@ -3759,7 +3759,7 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>2174</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3774,7 +3774,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>62,71%</t>
+          <t>58,36%</t>
         </is>
       </c>
     </row>
@@ -4822,12 +4822,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>5003</t>
+          <t>4753</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>9715</t>
+          <t>9626</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4837,12 +4837,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>46,1%</t>
+          <t>43,79%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>89,53%</t>
+          <t>88,7%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4857,12 +4857,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>7815</t>
+          <t>7938</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>12473</t>
+          <t>12604</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4872,12 +4872,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>58,9%</t>
+          <t>59,83%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>94,01%</t>
+          <t>95,0%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4892,12 +4892,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>14533</t>
+          <t>14160</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>21368</t>
+          <t>21131</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4907,12 +4907,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>60,25%</t>
+          <t>58,71%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>88,59%</t>
+          <t>87,61%</t>
         </is>
       </c>
     </row>
@@ -4940,7 +4940,7 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>3453</t>
+          <t>3732</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4955,7 +4955,7 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>31,82%</t>
+          <t>34,39%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -5010,7 +5010,7 @@
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>4285</t>
+          <t>4337</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5025,7 +5025,7 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>17,77%</t>
+          <t>17,98%</t>
         </is>
       </c>
     </row>
@@ -5048,12 +5048,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>475</t>
+          <t>486</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>4900</t>
+          <t>5226</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5063,12 +5063,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>45,15%</t>
+          <t>48,15%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>453</t>
+          <t>463</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>5331</t>
+          <t>5649</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>22,1%</t>
+          <t>23,42%</t>
         </is>
       </c>
     </row>
@@ -5201,7 +5201,7 @@
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>2270</t>
+          <t>2825</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5216,7 +5216,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>21,29%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5236,7 +5236,7 @@
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>2104</t>
+          <t>2610</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5251,7 +5251,7 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>10,82%</t>
         </is>
       </c>
     </row>
@@ -5309,12 +5309,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>390</t>
+          <t>379</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>5092</t>
+          <t>4935</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5324,12 +5324,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>38,38%</t>
+          <t>37,19%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5344,12 +5344,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>356</t>
+          <t>378</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>5576</t>
+          <t>5225</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5359,12 +5359,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>23,12%</t>
+          <t>21,66%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP16CS1_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP16CS1_2023-Clase-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -725,27 +725,27 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>1505</t>
+          <t>1121</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>345</t>
+          <t>206</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2226</t>
+          <t>1737</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>67,6%</t>
+          <t>64,53%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -760,27 +760,27 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1395</t>
+          <t>1484</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>301</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>2102</t>
+          <t>2250</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>66,38%</t>
+          <t>65,98%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -795,27 +795,27 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>2900</t>
+          <t>2605</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>974</t>
+          <t>927</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4328</t>
+          <t>3987</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>67,01%</t>
+          <t>65,34%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>22,51%</t>
+          <t>23,24%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>721</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>1881</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>32,4%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>84,51%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>766</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1949</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>34,02%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>86,63%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>721</t>
+          <t>765</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
@@ -918,12 +918,12 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2603</t>
+          <t>2631</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>19,2%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>60,15%</t>
+          <t>65,98%</t>
         </is>
       </c>
     </row>
@@ -1172,82 +1172,82 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>616</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1531</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>35,47%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>88,16%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>707</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>1798</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>33,62%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>85,56%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>707</t>
+          <t>616</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2893</t>
+          <t>2584</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>66,85%</t>
+          <t>64,8%</t>
         </is>
       </c>
     </row>
@@ -1290,17 +1290,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2226</t>
+          <t>1737</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2226</t>
+          <t>1737</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2226</t>
+          <t>1737</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1325,17 +1325,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2102</t>
+          <t>2250</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2102</t>
+          <t>2250</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2102</t>
+          <t>2250</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>4328</t>
+          <t>3987</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4328</t>
+          <t>3987</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4328</t>
+          <t>3987</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1407,27 +1407,27 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>2099</t>
+          <t>1138</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>466</t>
+          <t>341</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3749</t>
+          <t>1848</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>55,98%</t>
+          <t>61,57%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>18,45%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1442,27 +1442,27 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>1459</t>
+          <t>1983</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>401</t>
+          <t>397</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>2281</t>
+          <t>3720</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>63,95%</t>
+          <t>53,32%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>3557</t>
+          <t>3122</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1516</t>
+          <t>1087</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5276</t>
+          <t>4932</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>58,99%</t>
+          <t>56,06%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>25,14%</t>
+          <t>19,52%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>87,5%</t>
+          <t>88,56%</t>
         </is>
       </c>
     </row>
@@ -1628,72 +1628,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>1650</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>3283</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>44,02%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>87,56%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1737</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3323</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>46,68%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>89,34%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,7 +1703,7 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1650</t>
+          <t>1737</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
@@ -1713,12 +1713,12 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>3890</t>
+          <t>3944</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>27,37%</t>
+          <t>31,19%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>64,51%</t>
+          <t>70,83%</t>
         </is>
       </c>
     </row>
@@ -1741,82 +1741,82 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>407</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1507</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>22,01%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>81,55%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>464</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>1912</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>20,34%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>83,81%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>464</t>
+          <t>407</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
@@ -1826,12 +1826,12 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2204</t>
+          <t>2106</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
@@ -1841,7 +1841,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>36,55%</t>
+          <t>37,83%</t>
         </is>
       </c>
     </row>
@@ -1854,82 +1854,82 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>303</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1374</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>16,42%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>74,37%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>358</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>1710</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>15,71%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>74,97%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>358</t>
+          <t>303</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
@@ -1939,12 +1939,12 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1775</t>
+          <t>1938</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
@@ -1954,7 +1954,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>29,44%</t>
+          <t>34,81%</t>
         </is>
       </c>
     </row>
@@ -1972,17 +1972,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3749</t>
+          <t>1848</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3749</t>
+          <t>1848</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3749</t>
+          <t>1848</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2007,17 +2007,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2281</t>
+          <t>3720</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2281</t>
+          <t>3720</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2281</t>
+          <t>3720</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2042,17 +2042,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>6030</t>
+          <t>5569</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>6030</t>
+          <t>5569</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>6030</t>
+          <t>5569</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2084,64 +2084,64 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>298</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>1130</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>1029</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>396</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
           <t>—%</t>
@@ -2159,7 +2159,7 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1526</t>
+          <t>1328</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
@@ -2649,57 +2649,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>298</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>298</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>298</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>1130</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>1130</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>1130</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>396</t>
+          <t>1029</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>396</t>
+          <t>1029</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>396</t>
+          <t>1029</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1526</t>
+          <t>1328</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1526</t>
+          <t>1328</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1526</t>
+          <t>1328</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2766,72 +2766,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>3353</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>901</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>4303</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>77,92%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>20,93%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>1954</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>1400</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>3896</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>1356</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>4832</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>80,64%</t>
-        </is>
-      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>28,06%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,27 +2841,27 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>5850</t>
+          <t>4753</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3421</t>
+          <t>2160</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>6786</t>
+          <t>5703</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>86,21%</t>
+          <t>83,34%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>50,42%</t>
+          <t>37,88%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -3218,82 +3218,82 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>950</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3406</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>22,08%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>79,16%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>936</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>3476</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>19,36%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>71,94%</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>936</t>
+          <t>950</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
@@ -3303,12 +3303,12 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3367</t>
+          <t>3543</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
@@ -3318,7 +3318,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>49,62%</t>
+          <t>62,12%</t>
         </is>
       </c>
     </row>
@@ -3331,57 +3331,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>4303</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>4303</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>4303</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>1954</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>1954</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>1954</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>4832</t>
+          <t>1400</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>4832</t>
+          <t>1400</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>4832</t>
+          <t>1400</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3406,17 +3406,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>6786</t>
+          <t>5703</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>6786</t>
+          <t>5703</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>6786</t>
+          <t>5703</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3448,74 +3448,74 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>1439</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>603</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>1415</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>42,63%</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>525</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>1164</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>45,07%</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>2311</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q28" s="2" t="inlineStr">
         <is>
           <t>5</t>
@@ -3523,27 +3523,27 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>2914</t>
+          <t>1963</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1467</t>
+          <t>829</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>3726</t>
+          <t>2603</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>78,22%</t>
+          <t>75,43%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>39,37%</t>
+          <t>31,83%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -3561,74 +3561,74 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>350</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>1415</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>24,76%</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>258</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>1164</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>22,15%</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P29" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q29" s="2" t="inlineStr">
         <is>
           <t>1</t>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>258</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
@@ -3646,12 +3646,12 @@
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1511</t>
+          <t>1232</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
@@ -3661,7 +3661,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>40,56%</t>
+          <t>47,31%</t>
         </is>
       </c>
     </row>
@@ -3674,74 +3674,74 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>461</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>1415</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>32,61%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>382</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>1164</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>32,79%</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N30" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O30" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P30" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q30" s="2" t="inlineStr">
         <is>
           <t>1</t>
@@ -3749,7 +3749,7 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>461</t>
+          <t>382</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>2174</t>
+          <t>1651</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
@@ -3774,7 +3774,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>58,36%</t>
+          <t>63,43%</t>
         </is>
       </c>
     </row>
@@ -4013,57 +4013,57 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>1439</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>1439</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>1439</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>1415</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>1415</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>1415</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>2311</t>
+          <t>1164</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>2311</t>
+          <t>1164</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>2311</t>
+          <t>1164</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,17 +4088,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>3726</t>
+          <t>2603</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>3726</t>
+          <t>2603</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>3726</t>
+          <t>2603</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4130,64 +4130,64 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>1321</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>379</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>338</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K34" s="2" t="inlineStr">
-        <is>
-          <t>1346</t>
-        </is>
-      </c>
-      <c r="L34" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N34" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
           <t>—%</t>
@@ -4205,7 +4205,7 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>1725</t>
+          <t>1659</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
@@ -4695,57 +4695,57 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>1321</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>1321</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>1321</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>379</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>379</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>379</t>
-        </is>
-      </c>
-      <c r="G39" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H39" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I39" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J39" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>1346</t>
+          <t>338</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>1346</t>
+          <t>338</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>1346</t>
+          <t>338</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4770,17 +4770,17 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>1725</t>
+          <t>1659</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>1725</t>
+          <t>1659</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>1725</t>
+          <t>1659</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4812,72 +4812,72 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>8670</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>5940</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>10258</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>79,2%</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>54,26%</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>93,7%</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>7669</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>4753</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>9626</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr">
-        <is>
-          <t>70,67%</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>43,79%</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>88,7%</t>
-        </is>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>10803</t>
+          <t>6760</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>7938</t>
+          <t>3723</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>12604</t>
+          <t>8798</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>81,42%</t>
+          <t>68,27%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>59,83%</t>
+          <t>37,6%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>88,85%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4887,32 +4887,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>18472</t>
+          <t>15430</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>14160</t>
+          <t>11806</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>21131</t>
+          <t>18142</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>76,59%</t>
+          <t>74,01%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>58,71%</t>
+          <t>56,63%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>87,61%</t>
+          <t>87,02%</t>
         </is>
       </c>
     </row>
@@ -4925,72 +4925,72 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>1071</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>3732</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t>9,87%</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>34,39%</t>
-        </is>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3833</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>38,71%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5000,7 +5000,7 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>1071</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
@@ -5010,12 +5010,12 @@
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>4337</t>
+          <t>3980</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
@@ -5025,7 +5025,7 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>17,98%</t>
+          <t>19,09%</t>
         </is>
       </c>
     </row>
@@ -5038,72 +5038,72 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>2112</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>486</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>5226</t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="inlineStr">
-        <is>
-          <t>19,46%</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>4,48%</t>
-        </is>
-      </c>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t>48,15%</t>
-        </is>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2118</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>381</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5027</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>21,39%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>50,77%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5113,32 +5113,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>2112</t>
+          <t>2119</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>463</t>
+          <t>397</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>5649</t>
+          <t>5917</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>28,38%</t>
         </is>
       </c>
     </row>
@@ -5151,82 +5151,82 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>407</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2372</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>21,67%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K43" s="2" t="inlineStr">
-        <is>
-          <t>464</t>
-        </is>
-      </c>
-      <c r="L43" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M43" s="2" t="inlineStr">
-        <is>
-          <t>2825</t>
-        </is>
-      </c>
-      <c r="N43" s="2" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="O43" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P43" s="2" t="inlineStr">
-        <is>
-          <t>21,29%</t>
-        </is>
-      </c>
-      <c r="Q43" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>464</t>
+          <t>407</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
@@ -5236,12 +5236,12 @@
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>2610</t>
+          <t>2100</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
@@ -5251,7 +5251,7 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>10,07%</t>
         </is>
       </c>
     </row>
@@ -5264,107 +5264,107 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1870</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>333</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4902</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>17,08%</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>44,78%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="K44" s="2" t="inlineStr">
-        <is>
-          <t>2001</t>
-        </is>
-      </c>
-      <c r="L44" s="2" t="inlineStr">
-        <is>
-          <t>379</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="inlineStr">
-        <is>
-          <t>4935</t>
-        </is>
-      </c>
-      <c r="N44" s="2" t="inlineStr">
-        <is>
-          <t>15,08%</t>
-        </is>
-      </c>
-      <c r="O44" s="2" t="inlineStr">
-        <is>
-          <t>2,86%</t>
-        </is>
-      </c>
-      <c r="P44" s="2" t="inlineStr">
-        <is>
-          <t>37,19%</t>
-        </is>
-      </c>
-      <c r="Q44" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>2001</t>
+          <t>1870</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>378</t>
+          <t>305</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>5225</t>
+          <t>5185</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>21,66%</t>
+          <t>24,87%</t>
         </is>
       </c>
     </row>
@@ -5377,57 +5377,57 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>10947</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>10947</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>10947</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>10852</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>10852</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>10852</t>
-        </is>
-      </c>
-      <c r="G45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J45" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>13268</t>
+          <t>9902</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>13268</t>
+          <t>9902</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>13268</t>
+          <t>9902</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5452,17 +5452,17 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>24120</t>
+          <t>20849</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>24120</t>
+          <t>20849</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>24120</t>
+          <t>20849</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
